--- a/projects/スキンケアPV/スキンケア商品PV構成案.xlsx
+++ b/projects/スキンケアPV/スキンケア商品PV構成案.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>乾燥肌：ツヤツヤ光る／普通肌：自然なマット／脂性肌：控えめに光る</t>
+          <t>**乾燥肌**：ツヤツヤ光る／**普通肌**：自然なマット／**脂性肌**：控えめに光る</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>乾燥肌：毛穴目立たずしっとり／普通肌：テクスチャなめらか／脂性肌：余分な皮脂消える</t>
+          <t>**乾燥肌**：毛穴目立たずしっとり／**普通肌**：テクスチャなめらか／**脂性肌**：余分な皮脂消える</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
